--- a/bml-license-keygen/output/BML许可证签发记录.xlsx
+++ b/bml-license-keygen/output/BML许可证签发记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>BML 许可证签发记录</t>
   </si>
@@ -62,7 +62,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>LIC-20260414-B502A419</t>
+    <t>LIC-20260415-EEFA925E</t>
   </si>
   <si>
     <t>BML</t>
@@ -77,16 +77,25 @@
     <t>api_gateway, enterprise, system, monitor</t>
   </si>
   <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>2027-04-14</t>
-  </si>
-  <si>
-    <t>2026-04-14 15:07:54</t>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2027-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-15 21:11:29</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>LIC-20260415-176C2199</t>
+  </si>
+  <si>
+    <t>api_gateway, enterprise, system, monitor, alert</t>
+  </si>
+  <si>
+    <t>2026-04-15 21:33:10</t>
   </si>
 </sst>
 </file>
@@ -96,7 +105,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -130,8 +139,16 @@
       <name val="Microsoft YaHei"/>
       <sz val="10.0"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,6 +183,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="4080FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor rgb="F5F7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="F5F7FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -194,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center" vertical="center"/>
@@ -209,6 +236,12 @@
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -217,22 +250,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="9.375" customWidth="true"/>
-    <col min="2" max="2" width="28.125" customWidth="true"/>
-    <col min="3" max="3" width="25.0" customWidth="true"/>
-    <col min="4" max="4" width="21.875" customWidth="true"/>
-    <col min="5" max="5" width="15.625" customWidth="true"/>
-    <col min="6" max="6" width="31.25" customWidth="true"/>
-    <col min="7" max="7" width="21.875" customWidth="true"/>
-    <col min="8" max="8" width="21.875" customWidth="true"/>
-    <col min="9" max="9" width="21.875" customWidth="true"/>
-    <col min="10" max="10" width="18.75" customWidth="true"/>
-    <col min="11" max="11" width="18.75" customWidth="true"/>
-    <col min="12" max="12" width="25.0" customWidth="true"/>
-    <col min="13" max="13" width="31.25" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="9.375"/>
+    <col min="2" max="2" customWidth="true" width="28.125"/>
+    <col min="3" max="3" customWidth="true" width="25.0"/>
+    <col min="4" max="4" customWidth="true" width="21.875"/>
+    <col min="5" max="5" customWidth="true" width="15.625"/>
+    <col min="6" max="6" customWidth="true" width="31.25"/>
+    <col min="7" max="7" customWidth="true" width="21.875"/>
+    <col min="8" max="8" customWidth="true" width="21.875"/>
+    <col min="9" max="9" customWidth="true" width="21.875"/>
+    <col min="10" max="10" customWidth="true" width="18.75"/>
+    <col min="11" max="11" customWidth="true" width="18.75"/>
+    <col min="12" max="12" customWidth="true" width="25.0"/>
+    <col min="13" max="13" customWidth="true" width="31.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="48.0" customHeight="true">
@@ -351,6 +384,47 @@
         <v>23</v>
       </c>
     </row>
+    <row r="5" ht="28.0" customHeight="true">
+      <c r="A5" t="n" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B5" t="s" s="6">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s" s="6">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="6">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s" s="6">
+        <v>25</v>
+      </c>
+      <c r="G5" t="n" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H5" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I5" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="J5" t="s" s="7">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s" s="7">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="7">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s" s="6">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:M3"/>
   <mergeCells count="2">

--- a/bml-license-keygen/output/BML许可证签发记录.xlsx
+++ b/bml-license-keygen/output/BML许可证签发记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
   <si>
     <t>BML 许可证签发记录</t>
   </si>
@@ -62,13 +62,13 @@
     <t>备注</t>
   </si>
   <si>
-    <t>LIC-20260415-EEFA925E</t>
-  </si>
-  <si>
-    <t>BML</t>
-  </si>
-  <si>
-    <t>BML-001</t>
+    <t>LIC-20260416-E0DD2AAA</t>
+  </si>
+  <si>
+    <t>大象飞</t>
+  </si>
+  <si>
+    <t>DXF-001</t>
   </si>
   <si>
     <t>2.0.0</t>
@@ -77,25 +77,40 @@
     <t>api_gateway, enterprise, system, monitor</t>
   </si>
   <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2027-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-15 21:11:29</t>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2027-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-16 14:03:22</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>LIC-20260415-176C2199</t>
+    <t>LIC-20260416-6003FCE6</t>
   </si>
   <si>
     <t>api_gateway, enterprise, system, monitor, alert</t>
   </si>
   <si>
-    <t>2026-04-15 21:33:10</t>
+    <t>2026-04-16 14:22:40</t>
+  </si>
+  <si>
+    <t>LIC-20260416-4C03617D</t>
+  </si>
+  <si>
+    <t>2027-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-16 15:13:34</t>
+  </si>
+  <si>
+    <t>LIC-20260416-5C419557</t>
+  </si>
+  <si>
+    <t>2026-04-16 16:03:41</t>
   </si>
 </sst>
 </file>
@@ -105,7 +120,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -130,6 +145,22 @@
       <sz val="11.0"/>
       <b val="true"/>
       <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -221,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center" vertical="center"/>
@@ -242,6 +273,18 @@
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -250,7 +293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="9.375"/>
@@ -425,6 +468,88 @@
         <v>23</v>
       </c>
     </row>
+    <row r="6" ht="28.0" customHeight="true">
+      <c r="A6" t="n" s="8">
+        <v>3.0</v>
+      </c>
+      <c r="B6" t="s" s="8">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s" s="8">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="8">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s" s="8">
+        <v>23</v>
+      </c>
+      <c r="G6" t="n" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="H6" t="n" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="I6" t="n" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="J6" t="s" s="9">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s" s="9">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="28.0" customHeight="true">
+      <c r="A7" t="n" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="B7" t="s" s="10">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s" s="10">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s" s="10">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="10">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s" s="10">
+        <v>23</v>
+      </c>
+      <c r="G7" t="n" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="H7" t="n" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="I7" t="n" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="J7" t="s" s="11">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s" s="11">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s" s="11">
+        <v>31</v>
+      </c>
+      <c r="M7" t="s" s="10">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:M3"/>
   <mergeCells count="2">

--- a/bml-license-keygen/output/BML许可证签发记录.xlsx
+++ b/bml-license-keygen/output/BML许可证签发记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>BML 许可证签发记录</t>
   </si>
@@ -111,6 +111,21 @@
   </si>
   <si>
     <t>2026-04-16 16:03:41</t>
+  </si>
+  <si>
+    <t>LIC-20260418-AA4977D1</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-18 15:45:23</t>
+  </si>
+  <si>
+    <t>LIC-20260418-53533FE7</t>
+  </si>
+  <si>
+    <t>2026-04-18 16:53:34</t>
   </si>
 </sst>
 </file>
@@ -120,7 +135,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -145,6 +160,22 @@
       <sz val="11.0"/>
       <b val="true"/>
       <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -252,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center" vertical="center"/>
@@ -285,6 +316,18 @@
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -293,7 +336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="9.375"/>
@@ -550,6 +593,88 @@
         <v>23</v>
       </c>
     </row>
+    <row r="8" ht="28.0" customHeight="true">
+      <c r="A8" t="n" s="12">
+        <v>5.0</v>
+      </c>
+      <c r="B8" t="s" s="12">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s" s="12">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="12">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s" s="12">
+        <v>23</v>
+      </c>
+      <c r="G8" t="n" s="12">
+        <v>3.0</v>
+      </c>
+      <c r="H8" t="n" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I8" t="n" s="12">
+        <v>2.0</v>
+      </c>
+      <c r="J8" t="s" s="13">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s" s="13">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s" s="13">
+        <v>34</v>
+      </c>
+      <c r="M8" t="s" s="12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="28.0" customHeight="true">
+      <c r="A9" t="n" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="B9" t="s" s="14">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s" s="14">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s" s="14">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="14">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s" s="14">
+        <v>23</v>
+      </c>
+      <c r="G9" t="n" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="H9" t="n" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="I9" t="n" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="J9" t="s" s="15">
+        <v>33</v>
+      </c>
+      <c r="K9" t="s" s="15">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s" s="15">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s" s="14">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:M3"/>
   <mergeCells count="2">

--- a/bml-license-keygen/output/BML许可证签发记录.xlsx
+++ b/bml-license-keygen/output/BML许可证签发记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
   <si>
     <t>BML 许可证签发记录</t>
   </si>
@@ -126,16 +126,92 @@
   </si>
   <si>
     <t>2026-04-18 16:53:34</t>
+  </si>
+  <si>
+    <t>LIC-20260420-7B1BE76D</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:25:38</t>
+  </si>
+  <si>
+    <t>LIC-20260420-240AFCEA</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:45:50</t>
+  </si>
+  <si>
+    <t>LIC-20260420-0F17BAC0</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:46:47</t>
+  </si>
+  <si>
+    <t>LIC-20260420-30DE1A8D</t>
+  </si>
+  <si>
+    <t>2026-04-20 14:58:34</t>
+  </si>
+  <si>
+    <t>LIC-20260420150507-368ADC93</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:05:07</t>
+  </si>
+  <si>
+    <t>2027-04-20 23:59:59</t>
+  </si>
+  <si>
+    <t>2026-04-20 15:05:09</t>
+  </si>
+  <si>
+    <t>LIC-20260420161411-9C1AFACC</t>
+  </si>
+  <si>
+    <t>2026-04-20 16:14:11</t>
+  </si>
+  <si>
+    <t>2026-04-20 16:14:13</t>
+  </si>
+  <si>
+    <t>LIC-20260420161441-53EEDDDC</t>
+  </si>
+  <si>
+    <t>2026-04-20 16:14:41</t>
+  </si>
+  <si>
+    <t>2026-04-20 16:14:42</t>
+  </si>
+  <si>
+    <t>LIC-20260420161518-8FB9D418</t>
+  </si>
+  <si>
+    <t>2026-04-20 16:15:18</t>
+  </si>
+  <si>
+    <t>2026-04-20 16:15:19</t>
+  </si>
+  <si>
+    <t>LIC-20260420161754-5761DEAE</t>
+  </si>
+  <si>
+    <t>2026-04-20 16:17:54</t>
+  </si>
+  <si>
+    <t>2026-04-20 16:17:56</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="34">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -160,6 +236,78 @@
       <sz val="11.0"/>
       <b val="true"/>
       <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -283,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center" vertical="center"/>
@@ -328,6 +476,60 @@
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -336,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="9.375"/>
@@ -675,6 +877,375 @@
         <v>23</v>
       </c>
     </row>
+    <row r="10" ht="28.0" customHeight="true">
+      <c r="A10" t="n" s="16">
+        <v>7.0</v>
+      </c>
+      <c r="B10" t="s" s="16">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s" s="16">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="16">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s" s="16">
+        <v>23</v>
+      </c>
+      <c r="G10" t="n" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="H10" t="n" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="I10" t="n" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="J10" t="s" s="17">
+        <v>38</v>
+      </c>
+      <c r="K10" t="s" s="17">
+        <v>28</v>
+      </c>
+      <c r="L10" t="s" s="17">
+        <v>39</v>
+      </c>
+      <c r="M10" t="s" s="16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="28.0" customHeight="true">
+      <c r="A11" t="n" s="18">
+        <v>8.0</v>
+      </c>
+      <c r="B11" t="s" s="18">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s" s="18">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s" s="18">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="18">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s" s="18">
+        <v>23</v>
+      </c>
+      <c r="G11" t="n" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="H11" t="n" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="I11" t="n" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="J11" t="s" s="19">
+        <v>38</v>
+      </c>
+      <c r="K11" t="s" s="19">
+        <v>28</v>
+      </c>
+      <c r="L11" t="s" s="19">
+        <v>41</v>
+      </c>
+      <c r="M11" t="s" s="18">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="28.0" customHeight="true">
+      <c r="A12" t="n" s="20">
+        <v>9.0</v>
+      </c>
+      <c r="B12" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s" s="20">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s" s="20">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="20">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="G12" t="n" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="H12" t="n" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="I12" t="n" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="J12" t="s" s="21">
+        <v>38</v>
+      </c>
+      <c r="K12" t="s" s="21">
+        <v>28</v>
+      </c>
+      <c r="L12" t="s" s="21">
+        <v>43</v>
+      </c>
+      <c r="M12" t="s" s="20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="28.0" customHeight="true">
+      <c r="A13" t="n" s="22">
+        <v>10.0</v>
+      </c>
+      <c r="B13" t="s" s="22">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s" s="22">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s" s="22">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="22">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s" s="22">
+        <v>23</v>
+      </c>
+      <c r="G13" t="n" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="H13" t="n" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="I13" t="n" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="J13" t="s" s="23">
+        <v>38</v>
+      </c>
+      <c r="K13" t="s" s="23">
+        <v>28</v>
+      </c>
+      <c r="L13" t="s" s="23">
+        <v>45</v>
+      </c>
+      <c r="M13" t="s" s="22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" ht="28.0" customHeight="true">
+      <c r="A14" t="n" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="B14" t="s" s="24">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s" s="24">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s" s="24">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="24">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s" s="24">
+        <v>23</v>
+      </c>
+      <c r="G14" t="n" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="H14" t="n" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="I14" t="n" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="J14" t="s" s="25">
+        <v>47</v>
+      </c>
+      <c r="K14" t="s" s="25">
+        <v>48</v>
+      </c>
+      <c r="L14" t="s" s="25">
+        <v>49</v>
+      </c>
+      <c r="M14" t="s" s="24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="28.0" customHeight="true">
+      <c r="A15" t="n" s="26">
+        <v>12.0</v>
+      </c>
+      <c r="B15" t="s" s="26">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s" s="26">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s" s="26">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="26">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s" s="26">
+        <v>23</v>
+      </c>
+      <c r="G15" t="n" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="H15" t="n" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="I15" t="n" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="J15" t="s" s="27">
+        <v>51</v>
+      </c>
+      <c r="K15" t="s" s="27">
+        <v>48</v>
+      </c>
+      <c r="L15" t="s" s="27">
+        <v>52</v>
+      </c>
+      <c r="M15" t="s" s="26">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" ht="28.0" customHeight="true">
+      <c r="A16" t="n" s="28">
+        <v>13.0</v>
+      </c>
+      <c r="B16" t="s" s="28">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s" s="28">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s" s="28">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="28">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s" s="28">
+        <v>23</v>
+      </c>
+      <c r="G16" t="n" s="28">
+        <v>1.0</v>
+      </c>
+      <c r="H16" t="n" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="I16" t="n" s="28">
+        <v>1.0</v>
+      </c>
+      <c r="J16" t="s" s="29">
+        <v>54</v>
+      </c>
+      <c r="K16" t="s" s="29">
+        <v>48</v>
+      </c>
+      <c r="L16" t="s" s="29">
+        <v>55</v>
+      </c>
+      <c r="M16" t="s" s="28">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" ht="28.0" customHeight="true">
+      <c r="A17" t="n" s="30">
+        <v>14.0</v>
+      </c>
+      <c r="B17" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s" s="30">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="30">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s" s="30">
+        <v>23</v>
+      </c>
+      <c r="G17" t="n" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="H17" t="n" s="30">
+        <v>0.0</v>
+      </c>
+      <c r="I17" t="n" s="30">
+        <v>1.0</v>
+      </c>
+      <c r="J17" t="s" s="31">
+        <v>57</v>
+      </c>
+      <c r="K17" t="s" s="31">
+        <v>48</v>
+      </c>
+      <c r="L17" t="s" s="31">
+        <v>58</v>
+      </c>
+      <c r="M17" t="s" s="30">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" ht="28.0" customHeight="true">
+      <c r="A18" t="n" s="32">
+        <v>15.0</v>
+      </c>
+      <c r="B18" t="s" s="32">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s" s="32">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s" s="32">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="32">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s" s="32">
+        <v>23</v>
+      </c>
+      <c r="G18" t="n" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="H18" t="n" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="I18" t="n" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="J18" t="s" s="33">
+        <v>60</v>
+      </c>
+      <c r="K18" t="s" s="33">
+        <v>48</v>
+      </c>
+      <c r="L18" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="M18" t="s" s="32">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:M3"/>
   <mergeCells count="2">

--- a/bml-license-keygen/output/BML许可证签发记录.xlsx
+++ b/bml-license-keygen/output/BML许可证签发记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="89">
   <si>
     <t>BML 许可证签发记录</t>
   </si>
@@ -201,6 +201,87 @@
   </si>
   <si>
     <t>2026-04-20 16:17:56</t>
+  </si>
+  <si>
+    <t>LIC-20260425152427-186B155C</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:24:27</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:24:29</t>
+  </si>
+  <si>
+    <t>LIC-20260425153434-69791AA6</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:34:34</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:34:35</t>
+  </si>
+  <si>
+    <t>LIC-20260425153543-F1153DD6</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:35:43</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:35:44</t>
+  </si>
+  <si>
+    <t>LIC-20260425154202-6023F956</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:42:02</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:42:03</t>
+  </si>
+  <si>
+    <t>LIC-20260425155331-4DEFCFEF</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:53:31</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:53:32</t>
+  </si>
+  <si>
+    <t>LIC-20260425155413-351CBA27</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:54:13</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:54:14</t>
+  </si>
+  <si>
+    <t>LIC-20260425155502-C830A122</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:55:02</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:55:03</t>
+  </si>
+  <si>
+    <t>LIC-20260425155539-A20223CA</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:55:39</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:55:40</t>
+  </si>
+  <si>
+    <t>LIC-20260425155613-8B37F5ED</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:56:13</t>
+  </si>
+  <si>
+    <t>2026-04-25 15:56:14</t>
   </si>
 </sst>
 </file>
@@ -211,7 +292,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="52">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -236,6 +317,78 @@
       <sz val="11.0"/>
       <b val="true"/>
       <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -431,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center" vertical="center"/>
@@ -530,6 +683,60 @@
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="165" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="47" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="165" fontId="51" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -538,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="9.375"/>
@@ -1246,6 +1453,375 @@
         <v>23</v>
       </c>
     </row>
+    <row r="19" ht="28.0" customHeight="true">
+      <c r="A19" t="n" s="34">
+        <v>16.0</v>
+      </c>
+      <c r="B19" t="s" s="34">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s" s="34">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s" s="34">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="34">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s" s="34">
+        <v>23</v>
+      </c>
+      <c r="G19" t="n" s="34">
+        <v>1.0</v>
+      </c>
+      <c r="H19" t="n" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I19" t="n" s="34">
+        <v>1.0</v>
+      </c>
+      <c r="J19" t="s" s="35">
+        <v>63</v>
+      </c>
+      <c r="K19" t="s" s="35">
+        <v>48</v>
+      </c>
+      <c r="L19" t="s" s="35">
+        <v>64</v>
+      </c>
+      <c r="M19" t="s" s="34">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="28.0" customHeight="true">
+      <c r="A20" t="n" s="36">
+        <v>17.0</v>
+      </c>
+      <c r="B20" t="s" s="36">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s" s="36">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s" s="36">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="36">
+        <v>18</v>
+      </c>
+      <c r="F20" t="s" s="36">
+        <v>23</v>
+      </c>
+      <c r="G20" t="n" s="36">
+        <v>2.0</v>
+      </c>
+      <c r="H20" t="n" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="I20" t="n" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="J20" t="s" s="37">
+        <v>66</v>
+      </c>
+      <c r="K20" t="s" s="37">
+        <v>48</v>
+      </c>
+      <c r="L20" t="s" s="37">
+        <v>67</v>
+      </c>
+      <c r="M20" t="s" s="36">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" ht="28.0" customHeight="true">
+      <c r="A21" t="n" s="38">
+        <v>18.0</v>
+      </c>
+      <c r="B21" t="s" s="38">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s" s="38">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="38">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s" s="38">
+        <v>23</v>
+      </c>
+      <c r="G21" t="n" s="38">
+        <v>1.0</v>
+      </c>
+      <c r="H21" t="n" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="I21" t="n" s="38">
+        <v>1.0</v>
+      </c>
+      <c r="J21" t="s" s="39">
+        <v>69</v>
+      </c>
+      <c r="K21" t="s" s="39">
+        <v>48</v>
+      </c>
+      <c r="L21" t="s" s="39">
+        <v>70</v>
+      </c>
+      <c r="M21" t="s" s="38">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" ht="28.0" customHeight="true">
+      <c r="A22" t="n" s="40">
+        <v>19.0</v>
+      </c>
+      <c r="B22" t="s" s="40">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s" s="40">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s" s="40">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="40">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s" s="40">
+        <v>23</v>
+      </c>
+      <c r="G22" t="n" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H22" t="n" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I22" t="n" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="J22" t="s" s="41">
+        <v>72</v>
+      </c>
+      <c r="K22" t="s" s="41">
+        <v>48</v>
+      </c>
+      <c r="L22" t="s" s="41">
+        <v>73</v>
+      </c>
+      <c r="M22" t="s" s="40">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" ht="28.0" customHeight="true">
+      <c r="A23" t="n" s="42">
+        <v>20.0</v>
+      </c>
+      <c r="B23" t="s" s="42">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s" s="42">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s" s="42">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="42">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s" s="42">
+        <v>23</v>
+      </c>
+      <c r="G23" t="n" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="H23" t="n" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="I23" t="n" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="J23" t="s" s="43">
+        <v>75</v>
+      </c>
+      <c r="K23" t="s" s="43">
+        <v>48</v>
+      </c>
+      <c r="L23" t="s" s="43">
+        <v>76</v>
+      </c>
+      <c r="M23" t="s" s="42">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" ht="28.0" customHeight="true">
+      <c r="A24" t="n" s="44">
+        <v>21.0</v>
+      </c>
+      <c r="B24" t="s" s="44">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s" s="44">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s" s="44">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="44">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s" s="44">
+        <v>23</v>
+      </c>
+      <c r="G24" t="n" s="44">
+        <v>2.0</v>
+      </c>
+      <c r="H24" t="n" s="44">
+        <v>0.0</v>
+      </c>
+      <c r="I24" t="n" s="44">
+        <v>1.0</v>
+      </c>
+      <c r="J24" t="s" s="45">
+        <v>78</v>
+      </c>
+      <c r="K24" t="s" s="45">
+        <v>48</v>
+      </c>
+      <c r="L24" t="s" s="45">
+        <v>79</v>
+      </c>
+      <c r="M24" t="s" s="44">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="28.0" customHeight="true">
+      <c r="A25" t="n" s="46">
+        <v>22.0</v>
+      </c>
+      <c r="B25" t="s" s="46">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s" s="46">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s" s="46">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="46">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s" s="46">
+        <v>23</v>
+      </c>
+      <c r="G25" t="n" s="46">
+        <v>1.0</v>
+      </c>
+      <c r="H25" t="n" s="46">
+        <v>0.0</v>
+      </c>
+      <c r="I25" t="n" s="46">
+        <v>2.0</v>
+      </c>
+      <c r="J25" t="s" s="47">
+        <v>81</v>
+      </c>
+      <c r="K25" t="s" s="47">
+        <v>48</v>
+      </c>
+      <c r="L25" t="s" s="47">
+        <v>82</v>
+      </c>
+      <c r="M25" t="s" s="46">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" ht="28.0" customHeight="true">
+      <c r="A26" t="n" s="48">
+        <v>23.0</v>
+      </c>
+      <c r="B26" t="s" s="48">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s" s="48">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s" s="48">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s" s="48">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s" s="48">
+        <v>23</v>
+      </c>
+      <c r="G26" t="n" s="48">
+        <v>2.0</v>
+      </c>
+      <c r="H26" t="n" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="I26" t="n" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="J26" t="s" s="49">
+        <v>84</v>
+      </c>
+      <c r="K26" t="s" s="49">
+        <v>48</v>
+      </c>
+      <c r="L26" t="s" s="49">
+        <v>85</v>
+      </c>
+      <c r="M26" t="s" s="48">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" ht="28.0" customHeight="true">
+      <c r="A27" t="n" s="50">
+        <v>24.0</v>
+      </c>
+      <c r="B27" t="s" s="50">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s" s="50">
+        <v>16</v>
+      </c>
+      <c r="D27" t="s" s="50">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="50">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s" s="50">
+        <v>23</v>
+      </c>
+      <c r="G27" t="n" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="H27" t="n" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="I27" t="n" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="J27" t="s" s="51">
+        <v>87</v>
+      </c>
+      <c r="K27" t="s" s="51">
+        <v>48</v>
+      </c>
+      <c r="L27" t="s" s="51">
+        <v>88</v>
+      </c>
+      <c r="M27" t="s" s="50">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:M3"/>
   <mergeCells count="2">

--- a/bml-license-keygen/output/BML许可证签发记录.xlsx
+++ b/bml-license-keygen/output/BML许可证签发记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>BML 许可证签发记录</t>
   </si>
@@ -62,13 +62,13 @@
     <t>备注</t>
   </si>
   <si>
-    <t>LIC-20260430112817-7E810696</t>
-  </si>
-  <si>
-    <t>DXF</t>
-  </si>
-  <si>
-    <t>DXF-001</t>
+    <t>LIC-20260502184623-630B9A98</t>
+  </si>
+  <si>
+    <t>BML</t>
+  </si>
+  <si>
+    <t>BML-001</t>
   </si>
   <si>
     <t>2.0.0</t>
@@ -77,40 +77,55 @@
     <t/>
   </si>
   <si>
-    <t>2026-04-30 11:28:17</t>
-  </si>
-  <si>
-    <t>2027-04-30 23:59:59</t>
-  </si>
-  <si>
-    <t>2026-04-30 11:28:19</t>
-  </si>
-  <si>
-    <t>LIC-20260430113319-A368C6F2</t>
-  </si>
-  <si>
-    <t>2026-04-30 11:33:19</t>
-  </si>
-  <si>
-    <t>2026-04-30 11:33:20</t>
-  </si>
-  <si>
-    <t>LIC-20260430115138-62904EFB</t>
-  </si>
-  <si>
-    <t>2026-04-30 11:51:38</t>
-  </si>
-  <si>
-    <t>2026-04-30 11:51:39</t>
-  </si>
-  <si>
-    <t>LIC-20260430133554-0023D323</t>
-  </si>
-  <si>
-    <t>2026-04-30 13:35:54</t>
-  </si>
-  <si>
-    <t>2026-04-30 13:35:55</t>
+    <t>2026-05-02 18:46:23</t>
+  </si>
+  <si>
+    <t>2027-05-02 23:59:59</t>
+  </si>
+  <si>
+    <t>2026-05-02 18:46:25</t>
+  </si>
+  <si>
+    <t>LIC-20260502185705-1F8F3B8D</t>
+  </si>
+  <si>
+    <t>2026-05-02 18:57:05</t>
+  </si>
+  <si>
+    <t>2026-05-02 18:57:06</t>
+  </si>
+  <si>
+    <t>LIC-20260502185945-B999F374</t>
+  </si>
+  <si>
+    <t>2026-05-02 18:59:45</t>
+  </si>
+  <si>
+    <t>2026-05-02 18:59:46</t>
+  </si>
+  <si>
+    <t>LIC-20260502191153-33B9F996</t>
+  </si>
+  <si>
+    <t>2026-05-02 19:11:53</t>
+  </si>
+  <si>
+    <t>2026-05-02 19:11:54</t>
+  </si>
+  <si>
+    <t>LIC-20260502192522-94D6385A</t>
+  </si>
+  <si>
+    <t>2026-05-02 19:25:22</t>
+  </si>
+  <si>
+    <t>2026-05-02 19:25:23</t>
+  </si>
+  <si>
+    <t>LIC-20260502193107-D5478206</t>
+  </si>
+  <si>
+    <t>2026-05-02 19:31:07</t>
   </si>
 </sst>
 </file>
@@ -120,7 +135,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -145,6 +160,22 @@
       <sz val="11.0"/>
       <b val="true"/>
       <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -252,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center" vertical="center"/>
@@ -285,6 +316,18 @@
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -293,7 +336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="9.375"/>
@@ -447,7 +490,7 @@
         <v>19</v>
       </c>
       <c r="G5" t="n" s="6">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="H5" t="n" s="6">
         <v>1.0</v>
@@ -488,7 +531,7 @@
         <v>19</v>
       </c>
       <c r="G6" t="n" s="8">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="H6" t="n" s="8">
         <v>1.0</v>
@@ -529,7 +572,7 @@
         <v>19</v>
       </c>
       <c r="G7" t="n" s="10">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H7" t="n" s="10">
         <v>1.0</v>
@@ -547,6 +590,88 @@
         <v>31</v>
       </c>
       <c r="M7" t="s" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" ht="28.0" customHeight="true">
+      <c r="A8" t="n" s="12">
+        <v>5.0</v>
+      </c>
+      <c r="B8" t="s" s="12">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s" s="12">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="12">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s" s="12">
+        <v>19</v>
+      </c>
+      <c r="G8" t="n" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="H8" t="n" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I8" t="n" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="J8" t="s" s="13">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s" s="13">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s" s="13">
+        <v>34</v>
+      </c>
+      <c r="M8" t="s" s="12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="28.0" customHeight="true">
+      <c r="A9" t="n" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="B9" t="s" s="14">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s" s="14">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s" s="14">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="14">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s" s="14">
+        <v>19</v>
+      </c>
+      <c r="G9" t="n" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="H9" t="n" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="I9" t="n" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="J9" t="s" s="15">
+        <v>36</v>
+      </c>
+      <c r="K9" t="s" s="15">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s" s="15">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s" s="14">
         <v>19</v>
       </c>
     </row>

--- a/bml-license-keygen/output/BML许可证签发记录.xlsx
+++ b/bml-license-keygen/output/BML许可证签发记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
   <si>
     <t>BML 许可证签发记录</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>2026-05-02 19:31:07</t>
+  </si>
+  <si>
+    <t>LIC-20260507103953-53A97BFC</t>
+  </si>
+  <si>
+    <t>2026-05-07 10:39:53</t>
+  </si>
+  <si>
+    <t>2026-05-07 10:39:55</t>
   </si>
 </sst>
 </file>
@@ -135,7 +144,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -160,6 +169,14 @@
       <sz val="11.0"/>
       <b val="true"/>
       <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10.0"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -283,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center" vertical="center"/>
@@ -328,6 +345,12 @@
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -336,7 +359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="9.375"/>
@@ -675,6 +698,47 @@
         <v>19</v>
       </c>
     </row>
+    <row r="10" ht="28.0" customHeight="true">
+      <c r="A10" t="n" s="16">
+        <v>7.0</v>
+      </c>
+      <c r="B10" t="s" s="16">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s" s="16">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s" s="16">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="16">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s" s="16">
+        <v>19</v>
+      </c>
+      <c r="G10" t="n" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="H10" t="n" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="I10" t="n" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="J10" t="s" s="17">
+        <v>38</v>
+      </c>
+      <c r="K10" t="s" s="17">
+        <v>21</v>
+      </c>
+      <c r="L10" t="s" s="17">
+        <v>39</v>
+      </c>
+      <c r="M10" t="s" s="16">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:M3"/>
   <mergeCells count="2">
